--- a/data/tags/אלבומים חדשים/sites/yosmusic/2026-05-week02/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/2026-05-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אריק סיני – כל השירים היפים באמת</v>
+        <v>זארה לארסון Midnight Sun</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a8%d7%99%d7%a7-%d7%a1%d7%99%d7%a0%d7%99-%d7%9b%d7%9c-%d7%94%d7%a9%d7%99%d7%a8%d7%99%d7%9d-%d7%94%d7%99%d7%a4%d7%99%d7%9d-%d7%91%d7%90%d7%9e%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%96%d7%90%d7%a8%d7%94-%d7%9c%d7%90%d7%a8%d7%a1%d7%95%d7%9f-midnight-sun/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום "כל השירים היפים באמת” של אריק סיני הוא לא סתם אוסף קאברים אלא אלבום פרשנות. סיני לא מנסה “לעדכן” את השירים בכוח או להתחרות בביצועים המקוריים, אלא להפוך אותם לחלק מהעולם הפנימי והקולי שלו. זה אלבום שמבוסס פחות על</v>
+        <v>״אמרתי שעד גיל 20 אמלא אצטדיונים״,  שרה זארה לארסון ב־Midnight Sun, ואילו ב״Saturn’s Return״ אחד השרים היפים באלבום – . ״זה לא קרה, אז פשוט דחיתי את הדדליין״ השילוב המושך הזה בין נחישות לפגיעוּת זורם לאורך אלבום הדאנס־פופ המסחרר של</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אריק סיני – כל השירים היפים באמת</v>
+        <v>זארה לארסון Midnight Sun</v>
       </c>
     </row>
   </sheetData>
